--- a/Document/設計/画面項目.xlsx
+++ b/Document/設計/画面項目.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\設計\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD0AA35-7B4D-43B2-8F27-DA9082EDAD15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F777D0B6-DFDB-49AD-AA2A-788F2DAB9210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="2445" windowWidth="28170" windowHeight="14655" activeTab="1" xr2:uid="{AA7CD20D-EF31-43C6-91D3-14AF774D798D}"/>
+    <workbookView xWindow="38280" yWindow="5235" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AA7CD20D-EF31-43C6-91D3-14AF774D798D}"/>
   </bookViews>
   <sheets>
     <sheet name="変更履歴" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="70">
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="2">
@@ -467,16 +467,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>本日の3ヶ月後</t>
-    <rPh sb="0" eb="2">
-      <t>ホンジツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ゲツゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>必須・非必須記載</t>
     <rPh sb="0" eb="2">
       <t>ヒッス</t>
@@ -485,6 +475,114 @@
       <t>ヒヒッス</t>
     </rPh>
     <rPh sb="6" eb="8">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受験日</t>
+    <rPh sb="0" eb="3">
+      <t>ジュケンビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受験結果</t>
+    <rPh sb="0" eb="2">
+      <t>ジュケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Jukenbi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cmbResult</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンボボックス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空</t>
+    <rPh sb="0" eb="1">
+      <t>カラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受験日を更新</t>
+    <rPh sb="0" eb="3">
+      <t>ジュケンビ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受験結果更新</t>
+    <rPh sb="0" eb="2">
+      <t>ジュケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受験日と受験結果の項目を追加</t>
+    <rPh sb="0" eb="3">
+      <t>ジュケンビ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジュケン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[学習中,合格,不合格,合否待ち]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>年月or未定など自由記載</t>
+    <rPh sb="0" eb="1">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ミテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジユウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
       <t>キサイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -556,7 +654,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -749,6 +847,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -758,7 +865,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -766,9 +873,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
@@ -839,6 +943,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -863,8 +982,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C39BFF9-9DD3-4580-B273-F2E8174C0008}" name="テーブル1" displayName="テーブル1" ref="B3:C5" totalsRowShown="0">
-  <autoFilter ref="B3:C5" xr:uid="{5C39BFF9-9DD3-4580-B273-F2E8174C0008}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C39BFF9-9DD3-4580-B273-F2E8174C0008}" name="テーブル1" displayName="テーブル1" ref="B3:C6" totalsRowShown="0">
+  <autoFilter ref="B3:C6" xr:uid="{5C39BFF9-9DD3-4580-B273-F2E8174C0008}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{058DD02D-6238-4861-9A24-FF0DB7638319}" name="日時" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{9C85A13C-6A27-49C5-8B3B-2D930C6AF8D6}" name="内容"/>
@@ -1190,10 +1309,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD1C489-30B5-43CF-A9C9-E902360F1057}">
-  <dimension ref="B3:C5"/>
+  <dimension ref="B3:C6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.4">
@@ -1205,7 +1324,7 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B4" s="20">
+      <c r="B4" s="19">
         <v>46158</v>
       </c>
       <c r="C4" t="s">
@@ -1213,11 +1332,19 @@
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B5" s="20">
+      <c r="B5" s="19">
         <v>46171</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B6" s="19">
+        <v>46172</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1231,7 +1358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E22225-688F-464A-A19B-B132D7CFD18A}">
-  <dimension ref="B1:O15"/>
+  <dimension ref="B1:P17"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.125" customWidth="1"/>
@@ -1245,91 +1372,91 @@
     <col min="15" max="15" width="22.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B2" s="25"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="22" t="s">
+    <row r="1" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="23" t="s">
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="23"/>
-      <c r="O2" s="24"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="23"/>
     </row>
-    <row r="3" spans="2:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="9" t="s">
+    <row r="3" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B4" s="14" t="s">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="16"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="15"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B5" s="6" t="s">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1358,10 +1485,10 @@
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="7"/>
+      <c r="O5" s="6"/>
     </row>
-    <row r="6" spans="2:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+    <row r="6" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1390,10 +1517,10 @@
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-      <c r="O6" s="7"/>
+      <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="2:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="6"/>
+    <row r="7" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="5"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -1406,35 +1533,35 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-      <c r="O7" s="7"/>
+      <c r="O7" s="6"/>
     </row>
-    <row r="8" spans="2:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="17" t="s">
+    <row r="8" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="19"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="18"/>
     </row>
-    <row r="9" spans="2:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="6" t="s">
+    <row r="9" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>28</v>
@@ -1454,18 +1581,21 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="N9" s="1"/>
-      <c r="O9" s="21" t="s">
+      <c r="O9" s="20" t="s">
         <v>48</v>
       </c>
+      <c r="P9" s="30" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="10" spans="2:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+    <row r="10" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1498,12 +1628,12 @@
       <c r="N10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="O10" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="2:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="6" t="s">
+    <row r="11" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1532,12 +1662,12 @@
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="7" t="s">
+      <c r="O11" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B12" s="6" t="s">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1572,12 +1702,12 @@
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="7" t="s">
+      <c r="O12" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B13" s="6" t="s">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B13" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1606,12 +1736,12 @@
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="7" t="s">
+      <c r="O13" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1648,42 +1778,117 @@
         <v>36</v>
       </c>
       <c r="N14" s="1"/>
-      <c r="O14" s="7" t="s">
+      <c r="O14" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="2:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4" t="s">
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="5" t="s">
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="6" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B16" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N16" s="1"/>
+      <c r="O16" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N17" s="3"/>
+      <c r="O17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="P17" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Document/設計/画面項目.xlsx
+++ b/Document/設計/画面項目.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\設計\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F777D0B6-DFDB-49AD-AA2A-788F2DAB9210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9C06E0-0C7E-4EA8-9F3A-C619D67AA554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5235" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AA7CD20D-EF31-43C6-91D3-14AF774D798D}"/>
+    <workbookView xWindow="38280" yWindow="5235" windowWidth="29040" windowHeight="15720" xr2:uid="{AA7CD20D-EF31-43C6-91D3-14AF774D798D}"/>
   </bookViews>
   <sheets>
     <sheet name="変更履歴" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="71">
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="2">
@@ -584,6 +584,19 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最新の記録を参照</t>
+    <rPh sb="0" eb="2">
+      <t>サイシン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サンショウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1734,10 +1747,15 @@
       <c r="L13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="N13" s="1"/>
       <c r="O13" s="6" t="s">
         <v>51</v>
+      </c>
+      <c r="P13" s="30" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.4">
@@ -1780,6 +1798,9 @@
       <c r="N14" s="1"/>
       <c r="O14" s="6" t="s">
         <v>52</v>
+      </c>
+      <c r="P14" s="30" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.4">
@@ -1810,10 +1831,15 @@
       <c r="L15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="N15" s="1"/>
       <c r="O15" s="6" t="s">
         <v>53</v>
+      </c>
+      <c r="P15" s="30" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.4">

--- a/Document/設計/画面項目.xlsx
+++ b/Document/設計/画面項目.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\設計\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9C06E0-0C7E-4EA8-9F3A-C619D67AA554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F9FFC5-2390-403D-B5D5-DA2FA5580CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5235" windowWidth="29040" windowHeight="15720" xr2:uid="{AA7CD20D-EF31-43C6-91D3-14AF774D798D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA7CD20D-EF31-43C6-91D3-14AF774D798D}"/>
   </bookViews>
   <sheets>
     <sheet name="変更履歴" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="78">
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="2">
@@ -243,13 +243,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>本日</t>
-    <rPh sb="0" eb="2">
-      <t>ホンジツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>btnDisp_Click</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -588,15 +581,136 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>最新の記録を参照</t>
-    <rPh sb="0" eb="2">
-      <t>サイシン</t>
+    <t>登録モード</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録モードが新規[0]の場合は今日の日付で固定
+訂正モードの場合は今日までの日付が登録可能</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="41" eb="45">
+      <t>トウロクカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>lbltxtSelectMode</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今日の日付</t>
+    <rPh sb="0" eb="2">
+      <t>キョウ</t>
     </rPh>
     <rPh sb="3" eb="5">
-      <t>キロク</t>
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0（新規）</t>
+    <rPh sb="2" eb="4">
+      <t>シンキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1（訂正）</t>
+    <rPh sb="2" eb="4">
+      <t>テイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規モードの場合はボディを初期表示
+訂正モードの場合はExcelから引用表示</t>
+    <rPh sb="0" eb="2">
+      <t>シンキ</t>
     </rPh>
     <rPh sb="6" eb="8">
-      <t>サンショウ</t>
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>インヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>訂正モードの場合はExcelから引用表示</t>
+    <rPh sb="0" eb="2">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>インヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能改修分の反映</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイシュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンエイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -878,7 +992,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -942,6 +1056,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -957,20 +1077,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -995,8 +1106,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C39BFF9-9DD3-4580-B273-F2E8174C0008}" name="テーブル1" displayName="テーブル1" ref="B3:C6" totalsRowShown="0">
-  <autoFilter ref="B3:C6" xr:uid="{5C39BFF9-9DD3-4580-B273-F2E8174C0008}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C39BFF9-9DD3-4580-B273-F2E8174C0008}" name="テーブル1" displayName="テーブル1" ref="B3:C7" totalsRowShown="0">
+  <autoFilter ref="B3:C7" xr:uid="{5C39BFF9-9DD3-4580-B273-F2E8174C0008}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{058DD02D-6238-4861-9A24-FF0DB7638319}" name="日時" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{9C85A13C-6A27-49C5-8B3B-2D930C6AF8D6}" name="内容"/>
@@ -1322,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD1C489-30B5-43CF-A9C9-E902360F1057}">
-  <dimension ref="B3:C6"/>
+  <dimension ref="B3:C7"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="29.625" bestFit="1" customWidth="1"/>
@@ -1330,7 +1441,7 @@
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -1341,7 +1452,7 @@
         <v>46158</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.4">
@@ -1349,7 +1460,7 @@
         <v>46171</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.4">
@@ -1357,7 +1468,15 @@
         <v>46172</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B7" s="19">
+        <v>46259</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1371,40 +1490,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E22225-688F-464A-A19B-B132D7CFD18A}">
-  <dimension ref="B1:P17"/>
+  <dimension ref="B1:P18"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.125" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="12" max="12" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="36.75" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20.625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="45" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B2" s="24"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="21" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="22"/>
-      <c r="O2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="24"/>
+      <c r="O2" s="25"/>
     </row>
     <row r="3" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
@@ -1420,13 +1540,13 @@
         <v>28</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>37</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>38</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>2</v>
@@ -1441,13 +1561,13 @@
         <v>31</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.4">
@@ -1532,128 +1652,126 @@
       <c r="N6" s="1"/>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="5"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+    <row r="7" spans="2:16" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-      <c r="O7" s="6"/>
-    </row>
-    <row r="8" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="18"/>
+      <c r="O7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" s="28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="N8" s="1"/>
+      <c r="O8" s="6"/>
     </row>
     <row r="9" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
-      <c r="L9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>69</v>
-      </c>
+      <c r="O9" s="6"/>
     </row>
     <row r="10" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>47</v>
-      </c>
+      <c r="B10" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="18"/>
     </row>
     <row r="11" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="5" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>28</v>
@@ -1667,33 +1785,40 @@
       <c r="H11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="N11" s="1"/>
-      <c r="O11" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="O11" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="P11" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>27</v>
@@ -1701,33 +1826,31 @@
       <c r="H12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="1">
-        <v>4</v>
-      </c>
-      <c r="J12" s="1">
-        <v>9999</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O12" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B13" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>29</v>
@@ -1741,38 +1864,41 @@
       <c r="H13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1" t="s">
-        <v>32</v>
+      <c r="I13" s="1">
+        <v>4</v>
+      </c>
+      <c r="J13" s="1">
+        <v>9999</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="P13" s="30" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B14" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>27</v>
@@ -1780,41 +1906,33 @@
       <c r="H14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="1">
-        <v>3</v>
-      </c>
-      <c r="J14" s="1">
-        <v>100</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="P14" s="30" t="s">
-        <v>70</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="P14" s="22"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B15" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>9</v>
@@ -1825,35 +1943,39 @@
       <c r="H15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>32</v>
+      <c r="I15" s="1">
+        <v>3</v>
+      </c>
+      <c r="J15" s="1">
+        <v>100</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="P15" s="30" t="s">
-        <v>70</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="P15" s="22"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B16" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>28</v>
+      <c r="B16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>9</v>
@@ -1867,54 +1989,91 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="26" t="s">
-        <v>64</v>
+      <c r="L16" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="P16" s="22"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B17" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N17" s="1"/>
+      <c r="O17" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N18" s="3"/>
+      <c r="O18" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="17" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="P17" t="s">
-        <v>68</v>
+      <c r="P18" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
